--- a/2025_FP.xlsx
+++ b/2025_FP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgsafety-my.sharepoint.com/personal/adam_riman_mgsafety_com/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamr\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{324F6A9C-72FF-44B3-B854-3E35F72083EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33F2317F-70EB-436A-892C-5A0E08DE7B5E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50653520-097B-4EF8-BC7B-22D20A1DADC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Men" sheetId="2" r:id="rId1"/>
@@ -572,17 +572,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:Q321"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>21</v>
       </c>
@@ -635,7 +635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -688,7 +688,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -741,7 +741,7 @@
         <v>467.5</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -794,7 +794,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -847,7 +847,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -900,7 +900,7 @@
         <v>677.5</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -953,7 +953,7 @@
         <v>592.5</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
@@ -1006,7 +1006,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>482.5</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>497.5</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>7</v>
       </c>
@@ -1218,7 +1218,7 @@
         <v>522.5</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>612.5</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>9</v>
       </c>
@@ -1324,7 +1324,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>10</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>632.5</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>11</v>
       </c>
@@ -1430,7 +1430,7 @@
         <v>567.5</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>12</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>512.5</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>5</v>
       </c>
@@ -1536,7 +1536,7 @@
         <v>487.5</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
@@ -1589,7 +1589,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>7</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>537.5</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>8</v>
       </c>
@@ -1695,7 +1695,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>9</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>737.5</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>10</v>
       </c>
@@ -1801,7 +1801,7 @@
         <v>647.5</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>11</v>
       </c>
@@ -1854,7 +1854,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>12</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>527.5</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>5</v>
       </c>
@@ -1960,7 +1960,7 @@
         <v>497.5</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>6</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>522.5</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>7</v>
       </c>
@@ -2066,7 +2066,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>8</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>9</v>
       </c>
@@ -2172,7 +2172,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>10</v>
       </c>
@@ -2225,7 +2225,7 @@
         <v>662.5</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>11</v>
       </c>
@@ -2278,7 +2278,7 @@
         <v>597.5</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>12</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>5</v>
       </c>
@@ -2384,7 +2384,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>6</v>
       </c>
@@ -2437,7 +2437,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>7</v>
       </c>
@@ -2490,7 +2490,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>8</v>
       </c>
@@ -2543,7 +2543,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>9</v>
       </c>
@@ -2596,7 +2596,7 @@
         <v>787.5</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>10</v>
       </c>
@@ -2649,7 +2649,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>11</v>
       </c>
@@ -2702,7 +2702,7 @@
         <v>622.5</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>12</v>
       </c>
@@ -2755,7 +2755,7 @@
         <v>562.5</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>5</v>
       </c>
@@ -2808,7 +2808,7 @@
         <v>487.5</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>6</v>
       </c>
@@ -2861,7 +2861,7 @@
         <v>542.5</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>7</v>
       </c>
@@ -2914,7 +2914,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>8</v>
       </c>
@@ -2967,7 +2967,7 @@
         <v>702.5</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>9</v>
       </c>
@@ -3020,7 +3020,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>10</v>
       </c>
@@ -3073,7 +3073,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>11</v>
       </c>
@@ -3126,7 +3126,7 @@
         <v>652.5</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>12</v>
       </c>
@@ -3179,7 +3179,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>5</v>
       </c>
@@ -3232,7 +3232,7 @@
         <v>502.5</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>6</v>
       </c>
@@ -3285,7 +3285,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>7</v>
       </c>
@@ -3338,7 +3338,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>8</v>
       </c>
@@ -3391,7 +3391,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>9</v>
       </c>
@@ -3444,7 +3444,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>10</v>
       </c>
@@ -3497,7 +3497,7 @@
         <v>747.5</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>11</v>
       </c>
@@ -3550,7 +3550,7 @@
         <v>672.5</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>12</v>
       </c>
@@ -3603,7 +3603,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>5</v>
       </c>
@@ -3656,7 +3656,7 @@
         <v>512.5</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>6</v>
       </c>
@@ -3709,7 +3709,7 @@
         <v>567.5</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>7</v>
       </c>
@@ -3762,7 +3762,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>8</v>
       </c>
@@ -3815,7 +3815,7 @@
         <v>737.5</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>9</v>
       </c>
@@ -3868,7 +3868,7 @@
         <v>867.5</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>10</v>
       </c>
@@ -3921,7 +3921,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>11</v>
       </c>
@@ -3974,7 +3974,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>12</v>
       </c>
@@ -4027,7 +4027,7 @@
         <v>617.5</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>5</v>
       </c>
@@ -4080,7 +4080,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>6</v>
       </c>
@@ -4133,7 +4133,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>7</v>
       </c>
@@ -4186,7 +4186,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>8</v>
       </c>
@@ -4239,7 +4239,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>9</v>
       </c>
@@ -4292,7 +4292,7 @@
         <v>152.5</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>10</v>
       </c>
@@ -4345,7 +4345,7 @@
         <v>132.5</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>11</v>
       </c>
@@ -4398,7 +4398,7 @@
         <v>122.5</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>12</v>
       </c>
@@ -4451,7 +4451,7 @@
         <v>112.5</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>5</v>
       </c>
@@ -4504,7 +4504,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>6</v>
       </c>
@@ -4557,7 +4557,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>7</v>
       </c>
@@ -4610,7 +4610,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>8</v>
       </c>
@@ -4663,7 +4663,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>9</v>
       </c>
@@ -4716,7 +4716,7 @@
         <v>162.5</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>10</v>
       </c>
@@ -4769,7 +4769,7 @@
         <v>142.5</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>11</v>
       </c>
@@ -4822,7 +4822,7 @@
         <v>127.5</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>12</v>
       </c>
@@ -4875,7 +4875,7 @@
         <v>117.5</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>5</v>
       </c>
@@ -4928,7 +4928,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>6</v>
       </c>
@@ -4981,7 +4981,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>7</v>
       </c>
@@ -5034,7 +5034,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>8</v>
       </c>
@@ -5087,7 +5087,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>9</v>
       </c>
@@ -5140,7 +5140,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>10</v>
       </c>
@@ -5193,7 +5193,7 @@
         <v>147.5</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>11</v>
       </c>
@@ -5246,7 +5246,7 @@
         <v>132.5</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>12</v>
       </c>
@@ -5299,7 +5299,7 @@
         <v>122.5</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>5</v>
       </c>
@@ -5352,7 +5352,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>6</v>
       </c>
@@ -5405,7 +5405,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>7</v>
       </c>
@@ -5458,7 +5458,7 @@
         <v>207.5</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>8</v>
       </c>
@@ -5511,7 +5511,7 @@
         <v>242.5</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>9</v>
       </c>
@@ -5564,7 +5564,7 @@
         <v>282.5</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>10</v>
       </c>
@@ -5617,7 +5617,7 @@
         <v>247.5</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>11</v>
       </c>
@@ -5670,7 +5670,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>12</v>
       </c>
@@ -5723,7 +5723,7 @@
         <v>202.5</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>5</v>
       </c>
@@ -5788,7 +5788,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>6</v>
       </c>
@@ -5853,7 +5853,7 @@
         <v>197.5</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>7</v>
       </c>
@@ -5918,7 +5918,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>8</v>
       </c>
@@ -5983,7 +5983,7 @@
         <v>252.5</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>9</v>
       </c>
@@ -6048,7 +6048,7 @@
         <v>297.5</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>10</v>
       </c>
@@ -6113,7 +6113,7 @@
         <v>262.5</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>11</v>
       </c>
@@ -6178,7 +6178,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>12</v>
       </c>
@@ -6243,7 +6243,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>5</v>
       </c>
@@ -6296,7 +6296,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>6</v>
       </c>
@@ -6349,7 +6349,7 @@
         <v>207.5</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>7</v>
       </c>
@@ -6402,7 +6402,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>8</v>
       </c>
@@ -6455,7 +6455,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>9</v>
       </c>
@@ -6508,7 +6508,7 @@
         <v>312.5</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>10</v>
       </c>
@@ -6561,7 +6561,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>11</v>
       </c>
@@ -6614,7 +6614,7 @@
         <v>247.5</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>12</v>
       </c>
@@ -6667,7 +6667,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>5</v>
       </c>
@@ -6720,7 +6720,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>6</v>
       </c>
@@ -6773,7 +6773,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>7</v>
       </c>
@@ -6826,7 +6826,7 @@
         <v>132.5</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>8</v>
       </c>
@@ -6879,7 +6879,7 @@
         <v>152.5</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>9</v>
       </c>
@@ -6932,7 +6932,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>10</v>
       </c>
@@ -6985,7 +6985,7 @@
         <v>157.5</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>11</v>
       </c>
@@ -7038,7 +7038,7 @@
         <v>142.5</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>12</v>
       </c>
@@ -7091,7 +7091,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>5</v>
       </c>
@@ -7144,7 +7144,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>6</v>
       </c>
@@ -7197,7 +7197,7 @@
         <v>127.5</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>7</v>
       </c>
@@ -7250,7 +7250,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>8</v>
       </c>
@@ -7303,7 +7303,7 @@
         <v>162.5</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>9</v>
       </c>
@@ -7356,7 +7356,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>10</v>
       </c>
@@ -7409,7 +7409,7 @@
         <v>167.5</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>11</v>
       </c>
@@ -7462,7 +7462,7 @@
         <v>152.5</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>12</v>
       </c>
@@ -7515,7 +7515,7 @@
         <v>137.5</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>5</v>
       </c>
@@ -7568,7 +7568,7 @@
         <v>117.5</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>6</v>
       </c>
@@ -7621,7 +7621,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>7</v>
       </c>
@@ -7674,7 +7674,7 @@
         <v>142.5</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>8</v>
       </c>
@@ -7727,7 +7727,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>9</v>
       </c>
@@ -7780,7 +7780,7 @@
         <v>192.5</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>10</v>
       </c>
@@ -7833,7 +7833,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>11</v>
       </c>
@@ -7886,7 +7886,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>12</v>
       </c>
@@ -7939,7 +7939,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>5</v>
       </c>
@@ -8004,7 +8004,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>6</v>
       </c>
@@ -8069,7 +8069,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>7</v>
       </c>
@@ -8122,7 +8122,7 @@
         <v>242.5</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>8</v>
       </c>
@@ -8175,7 +8175,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>9</v>
       </c>
@@ -8228,7 +8228,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>10</v>
       </c>
@@ -8281,7 +8281,7 @@
         <v>292.5</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>11</v>
       </c>
@@ -8346,7 +8346,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>12</v>
       </c>
@@ -8411,7 +8411,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>5</v>
       </c>
@@ -8464,7 +8464,7 @@
         <v>197.5</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>6</v>
       </c>
@@ -8517,7 +8517,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>7</v>
       </c>
@@ -8570,7 +8570,7 @@
         <v>242.5</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>8</v>
       </c>
@@ -8623,7 +8623,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>9</v>
       </c>
@@ -8676,7 +8676,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>10</v>
       </c>
@@ -8729,7 +8729,7 @@
         <v>292.5</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>11</v>
       </c>
@@ -8782,7 +8782,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>12</v>
       </c>
@@ -8835,7 +8835,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>5</v>
       </c>
@@ -8900,7 +8900,7 @@
         <v>207.5</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>6</v>
       </c>
@@ -8965,7 +8965,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>7</v>
       </c>
@@ -9018,7 +9018,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>8</v>
       </c>
@@ -9071,7 +9071,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>9</v>
       </c>
@@ -9124,7 +9124,7 @@
         <v>352.5</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>10</v>
       </c>
@@ -9177,7 +9177,7 @@
         <v>307.5</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>11</v>
       </c>
@@ -9242,7 +9242,7 @@
         <v>277.5</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>12</v>
       </c>
@@ -9307,7 +9307,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="162" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -9326,7 +9326,7 @@
       <c r="P162" s="3"/>
       <c r="Q162" s="3"/>
     </row>
-    <row r="163" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -9345,7 +9345,7 @@
       <c r="P163" s="3"/>
       <c r="Q163" s="3"/>
     </row>
-    <row r="164" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -9364,7 +9364,7 @@
       <c r="P164" s="3"/>
       <c r="Q164" s="3"/>
     </row>
-    <row r="165" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -9383,7 +9383,7 @@
       <c r="P165" s="3"/>
       <c r="Q165" s="3"/>
     </row>
-    <row r="166" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -9402,7 +9402,7 @@
       <c r="P166" s="3"/>
       <c r="Q166" s="3"/>
     </row>
-    <row r="167" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -9421,7 +9421,7 @@
       <c r="P167" s="3"/>
       <c r="Q167" s="3"/>
     </row>
-    <row r="168" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -9440,7 +9440,7 @@
       <c r="P168" s="3"/>
       <c r="Q168" s="3"/>
     </row>
-    <row r="169" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -9459,7 +9459,7 @@
       <c r="P169" s="3"/>
       <c r="Q169" s="3"/>
     </row>
-    <row r="170" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -9478,7 +9478,7 @@
       <c r="P170" s="3"/>
       <c r="Q170" s="3"/>
     </row>
-    <row r="171" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -9497,7 +9497,7 @@
       <c r="P171" s="3"/>
       <c r="Q171" s="3"/>
     </row>
-    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -9516,7 +9516,7 @@
       <c r="P172" s="3"/>
       <c r="Q172" s="3"/>
     </row>
-    <row r="173" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -9535,7 +9535,7 @@
       <c r="P173" s="3"/>
       <c r="Q173" s="3"/>
     </row>
-    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -9554,7 +9554,7 @@
       <c r="P174" s="3"/>
       <c r="Q174" s="3"/>
     </row>
-    <row r="175" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -9573,7 +9573,7 @@
       <c r="P175" s="3"/>
       <c r="Q175" s="3"/>
     </row>
-    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -9592,7 +9592,7 @@
       <c r="P176" s="3"/>
       <c r="Q176" s="3"/>
     </row>
-    <row r="177" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -9611,7 +9611,7 @@
       <c r="P177" s="3"/>
       <c r="Q177" s="3"/>
     </row>
-    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -9630,7 +9630,7 @@
       <c r="P178" s="3"/>
       <c r="Q178" s="3"/>
     </row>
-    <row r="179" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -9649,7 +9649,7 @@
       <c r="P179" s="3"/>
       <c r="Q179" s="3"/>
     </row>
-    <row r="180" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -9668,7 +9668,7 @@
       <c r="P180" s="3"/>
       <c r="Q180" s="3"/>
     </row>
-    <row r="181" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -9687,7 +9687,7 @@
       <c r="P181" s="3"/>
       <c r="Q181" s="3"/>
     </row>
-    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -9706,7 +9706,7 @@
       <c r="P182" s="3"/>
       <c r="Q182" s="3"/>
     </row>
-    <row r="183" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -9725,7 +9725,7 @@
       <c r="P183" s="3"/>
       <c r="Q183" s="3"/>
     </row>
-    <row r="184" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -9744,7 +9744,7 @@
       <c r="P184" s="3"/>
       <c r="Q184" s="3"/>
     </row>
-    <row r="185" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -9763,7 +9763,7 @@
       <c r="P185" s="3"/>
       <c r="Q185" s="3"/>
     </row>
-    <row r="186" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -9782,7 +9782,7 @@
       <c r="P186" s="3"/>
       <c r="Q186" s="3"/>
     </row>
-    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -9801,7 +9801,7 @@
       <c r="P187" s="3"/>
       <c r="Q187" s="3"/>
     </row>
-    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -9820,7 +9820,7 @@
       <c r="P188" s="3"/>
       <c r="Q188" s="3"/>
     </row>
-    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -9839,7 +9839,7 @@
       <c r="P189" s="3"/>
       <c r="Q189" s="3"/>
     </row>
-    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -9858,7 +9858,7 @@
       <c r="P190" s="3"/>
       <c r="Q190" s="3"/>
     </row>
-    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -9877,7 +9877,7 @@
       <c r="P191" s="3"/>
       <c r="Q191" s="3"/>
     </row>
-    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -9896,7 +9896,7 @@
       <c r="P192" s="3"/>
       <c r="Q192" s="3"/>
     </row>
-    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -9915,7 +9915,7 @@
       <c r="P193" s="3"/>
       <c r="Q193" s="3"/>
     </row>
-    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -9934,7 +9934,7 @@
       <c r="P194" s="5"/>
       <c r="Q194" s="5"/>
     </row>
-    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -9953,7 +9953,7 @@
       <c r="P195" s="5"/>
       <c r="Q195" s="5"/>
     </row>
-    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -9972,7 +9972,7 @@
       <c r="P196" s="5"/>
       <c r="Q196" s="5"/>
     </row>
-    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -9991,7 +9991,7 @@
       <c r="P197" s="5"/>
       <c r="Q197" s="5"/>
     </row>
-    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -10010,7 +10010,7 @@
       <c r="P198" s="5"/>
       <c r="Q198" s="5"/>
     </row>
-    <row r="199" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -10029,7 +10029,7 @@
       <c r="P199" s="5"/>
       <c r="Q199" s="5"/>
     </row>
-    <row r="200" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -10048,7 +10048,7 @@
       <c r="P200" s="5"/>
       <c r="Q200" s="5"/>
     </row>
-    <row r="201" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -10067,7 +10067,7 @@
       <c r="P201" s="5"/>
       <c r="Q201" s="5"/>
     </row>
-    <row r="202" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -10086,7 +10086,7 @@
       <c r="P202" s="5"/>
       <c r="Q202" s="5"/>
     </row>
-    <row r="203" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -10105,7 +10105,7 @@
       <c r="P203" s="5"/>
       <c r="Q203" s="5"/>
     </row>
-    <row r="204" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -10124,7 +10124,7 @@
       <c r="P204" s="5"/>
       <c r="Q204" s="5"/>
     </row>
-    <row r="205" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
@@ -10143,7 +10143,7 @@
       <c r="P205" s="5"/>
       <c r="Q205" s="5"/>
     </row>
-    <row r="206" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
@@ -10162,7 +10162,7 @@
       <c r="P206" s="5"/>
       <c r="Q206" s="5"/>
     </row>
-    <row r="207" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
@@ -10181,7 +10181,7 @@
       <c r="P207" s="5"/>
       <c r="Q207" s="5"/>
     </row>
-    <row r="208" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
@@ -10200,7 +10200,7 @@
       <c r="P208" s="5"/>
       <c r="Q208" s="5"/>
     </row>
-    <row r="209" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -10219,7 +10219,7 @@
       <c r="P209" s="5"/>
       <c r="Q209" s="5"/>
     </row>
-    <row r="210" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
@@ -10238,7 +10238,7 @@
       <c r="P210" s="5"/>
       <c r="Q210" s="5"/>
     </row>
-    <row r="211" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
@@ -10257,7 +10257,7 @@
       <c r="P211" s="5"/>
       <c r="Q211" s="5"/>
     </row>
-    <row r="212" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
@@ -10276,7 +10276,7 @@
       <c r="P212" s="5"/>
       <c r="Q212" s="5"/>
     </row>
-    <row r="213" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
@@ -10295,7 +10295,7 @@
       <c r="P213" s="5"/>
       <c r="Q213" s="5"/>
     </row>
-    <row r="214" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
@@ -10314,7 +10314,7 @@
       <c r="P214" s="5"/>
       <c r="Q214" s="5"/>
     </row>
-    <row r="215" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
@@ -10333,7 +10333,7 @@
       <c r="P215" s="5"/>
       <c r="Q215" s="5"/>
     </row>
-    <row r="216" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
@@ -10352,7 +10352,7 @@
       <c r="P216" s="5"/>
       <c r="Q216" s="5"/>
     </row>
-    <row r="217" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
@@ -10371,7 +10371,7 @@
       <c r="P217" s="5"/>
       <c r="Q217" s="5"/>
     </row>
-    <row r="218" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
@@ -10390,7 +10390,7 @@
       <c r="P218" s="5"/>
       <c r="Q218" s="5"/>
     </row>
-    <row r="219" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
@@ -10409,7 +10409,7 @@
       <c r="P219" s="5"/>
       <c r="Q219" s="5"/>
     </row>
-    <row r="220" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
@@ -10428,7 +10428,7 @@
       <c r="P220" s="5"/>
       <c r="Q220" s="5"/>
     </row>
-    <row r="221" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
@@ -10447,7 +10447,7 @@
       <c r="P221" s="5"/>
       <c r="Q221" s="5"/>
     </row>
-    <row r="222" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="2"/>
@@ -10466,7 +10466,7 @@
       <c r="P222" s="5"/>
       <c r="Q222" s="5"/>
     </row>
-    <row r="223" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
       <c r="C223" s="2"/>
@@ -10485,7 +10485,7 @@
       <c r="P223" s="5"/>
       <c r="Q223" s="5"/>
     </row>
-    <row r="224" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="2"/>
@@ -10504,7 +10504,7 @@
       <c r="P224" s="5"/>
       <c r="Q224" s="5"/>
     </row>
-    <row r="225" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="2"/>
@@ -10523,7 +10523,7 @@
       <c r="P225" s="5"/>
       <c r="Q225" s="5"/>
     </row>
-    <row r="226" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
@@ -10542,7 +10542,7 @@
       <c r="P226" s="3"/>
       <c r="Q226" s="3"/>
     </row>
-    <row r="227" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
@@ -10561,7 +10561,7 @@
       <c r="P227" s="3"/>
       <c r="Q227" s="3"/>
     </row>
-    <row r="228" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="2"/>
@@ -10580,7 +10580,7 @@
       <c r="P228" s="3"/>
       <c r="Q228" s="3"/>
     </row>
-    <row r="229" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
@@ -10599,7 +10599,7 @@
       <c r="P229" s="3"/>
       <c r="Q229" s="3"/>
     </row>
-    <row r="230" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
@@ -10618,7 +10618,7 @@
       <c r="P230" s="3"/>
       <c r="Q230" s="3"/>
     </row>
-    <row r="231" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
@@ -10637,7 +10637,7 @@
       <c r="P231" s="3"/>
       <c r="Q231" s="3"/>
     </row>
-    <row r="232" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="2"/>
@@ -10656,7 +10656,7 @@
       <c r="P232" s="3"/>
       <c r="Q232" s="3"/>
     </row>
-    <row r="233" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="2"/>
@@ -10675,7 +10675,7 @@
       <c r="P233" s="3"/>
       <c r="Q233" s="3"/>
     </row>
-    <row r="234" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
@@ -10694,7 +10694,7 @@
       <c r="P234" s="5"/>
       <c r="Q234" s="5"/>
     </row>
-    <row r="235" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
@@ -10713,7 +10713,7 @@
       <c r="P235" s="5"/>
       <c r="Q235" s="5"/>
     </row>
-    <row r="236" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="2"/>
@@ -10732,7 +10732,7 @@
       <c r="P236" s="5"/>
       <c r="Q236" s="5"/>
     </row>
-    <row r="237" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2"/>
       <c r="B237" s="2"/>
       <c r="C237" s="2"/>
@@ -10751,7 +10751,7 @@
       <c r="P237" s="5"/>
       <c r="Q237" s="5"/>
     </row>
-    <row r="238" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="2"/>
@@ -10770,7 +10770,7 @@
       <c r="P238" s="5"/>
       <c r="Q238" s="5"/>
     </row>
-    <row r="239" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="2"/>
@@ -10789,7 +10789,7 @@
       <c r="P239" s="5"/>
       <c r="Q239" s="5"/>
     </row>
-    <row r="240" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
       <c r="C240" s="2"/>
@@ -10808,7 +10808,7 @@
       <c r="P240" s="5"/>
       <c r="Q240" s="5"/>
     </row>
-    <row r="241" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
       <c r="C241" s="2"/>
@@ -10827,7 +10827,7 @@
       <c r="P241" s="5"/>
       <c r="Q241" s="5"/>
     </row>
-    <row r="242" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2"/>
       <c r="B242" s="2"/>
       <c r="C242" s="2"/>
@@ -10846,7 +10846,7 @@
       <c r="P242" s="3"/>
       <c r="Q242" s="3"/>
     </row>
-    <row r="243" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="2"/>
@@ -10865,7 +10865,7 @@
       <c r="P243" s="3"/>
       <c r="Q243" s="3"/>
     </row>
-    <row r="244" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
       <c r="C244" s="2"/>
@@ -10884,7 +10884,7 @@
       <c r="P244" s="3"/>
       <c r="Q244" s="3"/>
     </row>
-    <row r="245" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="2"/>
@@ -10903,7 +10903,7 @@
       <c r="P245" s="3"/>
       <c r="Q245" s="3"/>
     </row>
-    <row r="246" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="2"/>
@@ -10922,7 +10922,7 @@
       <c r="P246" s="3"/>
       <c r="Q246" s="3"/>
     </row>
-    <row r="247" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
       <c r="C247" s="2"/>
@@ -10941,7 +10941,7 @@
       <c r="P247" s="3"/>
       <c r="Q247" s="3"/>
     </row>
-    <row r="248" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
       <c r="C248" s="2"/>
@@ -10960,7 +10960,7 @@
       <c r="P248" s="3"/>
       <c r="Q248" s="3"/>
     </row>
-    <row r="249" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
       <c r="C249" s="2"/>
@@ -10979,7 +10979,7 @@
       <c r="P249" s="3"/>
       <c r="Q249" s="3"/>
     </row>
-    <row r="250" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="2"/>
@@ -10998,7 +10998,7 @@
       <c r="P250" s="3"/>
       <c r="Q250" s="3"/>
     </row>
-    <row r="251" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
       <c r="C251" s="2"/>
@@ -11017,7 +11017,7 @@
       <c r="P251" s="3"/>
       <c r="Q251" s="3"/>
     </row>
-    <row r="252" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="2"/>
@@ -11036,7 +11036,7 @@
       <c r="P252" s="3"/>
       <c r="Q252" s="3"/>
     </row>
-    <row r="253" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="2"/>
@@ -11055,7 +11055,7 @@
       <c r="P253" s="3"/>
       <c r="Q253" s="3"/>
     </row>
-    <row r="254" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
@@ -11074,7 +11074,7 @@
       <c r="P254" s="3"/>
       <c r="Q254" s="3"/>
     </row>
-    <row r="255" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="2"/>
@@ -11093,7 +11093,7 @@
       <c r="P255" s="3"/>
       <c r="Q255" s="3"/>
     </row>
-    <row r="256" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="2"/>
@@ -11112,7 +11112,7 @@
       <c r="P256" s="3"/>
       <c r="Q256" s="3"/>
     </row>
-    <row r="257" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="2"/>
@@ -11131,7 +11131,7 @@
       <c r="P257" s="3"/>
       <c r="Q257" s="3"/>
     </row>
-    <row r="258" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="2"/>
@@ -11150,7 +11150,7 @@
       <c r="P258" s="5"/>
       <c r="Q258" s="5"/>
     </row>
-    <row r="259" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
       <c r="C259" s="2"/>
@@ -11169,7 +11169,7 @@
       <c r="P259" s="5"/>
       <c r="Q259" s="5"/>
     </row>
-    <row r="260" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
       <c r="C260" s="2"/>
@@ -11188,7 +11188,7 @@
       <c r="P260" s="5"/>
       <c r="Q260" s="5"/>
     </row>
-    <row r="261" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
       <c r="C261" s="2"/>
@@ -11207,7 +11207,7 @@
       <c r="P261" s="5"/>
       <c r="Q261" s="5"/>
     </row>
-    <row r="262" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
       <c r="C262" s="2"/>
@@ -11226,7 +11226,7 @@
       <c r="P262" s="5"/>
       <c r="Q262" s="5"/>
     </row>
-    <row r="263" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="2"/>
@@ -11245,7 +11245,7 @@
       <c r="P263" s="5"/>
       <c r="Q263" s="5"/>
     </row>
-    <row r="264" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
       <c r="C264" s="2"/>
@@ -11264,7 +11264,7 @@
       <c r="P264" s="5"/>
       <c r="Q264" s="5"/>
     </row>
-    <row r="265" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="2"/>
@@ -11283,7 +11283,7 @@
       <c r="P265" s="5"/>
       <c r="Q265" s="5"/>
     </row>
-    <row r="266" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2"/>
       <c r="B266" s="2"/>
       <c r="C266" s="2"/>
@@ -11302,7 +11302,7 @@
       <c r="P266" s="3"/>
       <c r="Q266" s="3"/>
     </row>
-    <row r="267" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2"/>
       <c r="B267" s="2"/>
       <c r="C267" s="2"/>
@@ -11321,7 +11321,7 @@
       <c r="P267" s="3"/>
       <c r="Q267" s="3"/>
     </row>
-    <row r="268" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2"/>
       <c r="B268" s="2"/>
       <c r="C268" s="2"/>
@@ -11340,7 +11340,7 @@
       <c r="P268" s="3"/>
       <c r="Q268" s="3"/>
     </row>
-    <row r="269" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2"/>
       <c r="B269" s="2"/>
       <c r="C269" s="2"/>
@@ -11359,7 +11359,7 @@
       <c r="P269" s="3"/>
       <c r="Q269" s="3"/>
     </row>
-    <row r="270" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2"/>
       <c r="B270" s="2"/>
       <c r="C270" s="2"/>
@@ -11378,7 +11378,7 @@
       <c r="P270" s="3"/>
       <c r="Q270" s="3"/>
     </row>
-    <row r="271" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2"/>
       <c r="B271" s="2"/>
       <c r="C271" s="2"/>
@@ -11397,7 +11397,7 @@
       <c r="P271" s="3"/>
       <c r="Q271" s="3"/>
     </row>
-    <row r="272" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2"/>
       <c r="B272" s="2"/>
       <c r="C272" s="2"/>
@@ -11416,7 +11416,7 @@
       <c r="P272" s="3"/>
       <c r="Q272" s="3"/>
     </row>
-    <row r="273" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2"/>
       <c r="B273" s="2"/>
       <c r="C273" s="2"/>
@@ -11435,7 +11435,7 @@
       <c r="P273" s="3"/>
       <c r="Q273" s="3"/>
     </row>
-    <row r="274" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2"/>
       <c r="B274" s="2"/>
       <c r="C274" s="2"/>
@@ -11454,7 +11454,7 @@
       <c r="P274" s="3"/>
       <c r="Q274" s="3"/>
     </row>
-    <row r="275" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2"/>
       <c r="B275" s="2"/>
       <c r="C275" s="2"/>
@@ -11473,7 +11473,7 @@
       <c r="P275" s="3"/>
       <c r="Q275" s="3"/>
     </row>
-    <row r="276" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2"/>
       <c r="B276" s="2"/>
       <c r="C276" s="2"/>
@@ -11492,7 +11492,7 @@
       <c r="P276" s="3"/>
       <c r="Q276" s="3"/>
     </row>
-    <row r="277" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2"/>
       <c r="B277" s="2"/>
       <c r="C277" s="2"/>
@@ -11511,7 +11511,7 @@
       <c r="P277" s="3"/>
       <c r="Q277" s="3"/>
     </row>
-    <row r="278" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2"/>
       <c r="B278" s="2"/>
       <c r="C278" s="2"/>
@@ -11530,7 +11530,7 @@
       <c r="P278" s="3"/>
       <c r="Q278" s="3"/>
     </row>
-    <row r="279" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2"/>
       <c r="B279" s="2"/>
       <c r="C279" s="2"/>
@@ -11549,7 +11549,7 @@
       <c r="P279" s="3"/>
       <c r="Q279" s="3"/>
     </row>
-    <row r="280" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2"/>
       <c r="B280" s="2"/>
       <c r="C280" s="2"/>
@@ -11568,7 +11568,7 @@
       <c r="P280" s="3"/>
       <c r="Q280" s="3"/>
     </row>
-    <row r="281" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2"/>
       <c r="B281" s="2"/>
       <c r="C281" s="2"/>
@@ -11587,7 +11587,7 @@
       <c r="P281" s="3"/>
       <c r="Q281" s="3"/>
     </row>
-    <row r="282" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2"/>
       <c r="B282" s="2"/>
       <c r="C282" s="2"/>
@@ -11606,7 +11606,7 @@
       <c r="P282" s="3"/>
       <c r="Q282" s="3"/>
     </row>
-    <row r="283" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2"/>
       <c r="B283" s="2"/>
       <c r="C283" s="2"/>
@@ -11625,7 +11625,7 @@
       <c r="P283" s="3"/>
       <c r="Q283" s="3"/>
     </row>
-    <row r="284" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
       <c r="C284" s="2"/>
@@ -11644,7 +11644,7 @@
       <c r="P284" s="3"/>
       <c r="Q284" s="3"/>
     </row>
-    <row r="285" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2"/>
       <c r="B285" s="2"/>
       <c r="C285" s="2"/>
@@ -11663,7 +11663,7 @@
       <c r="P285" s="3"/>
       <c r="Q285" s="3"/>
     </row>
-    <row r="286" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2"/>
       <c r="B286" s="2"/>
       <c r="C286" s="2"/>
@@ -11682,7 +11682,7 @@
       <c r="P286" s="3"/>
       <c r="Q286" s="3"/>
     </row>
-    <row r="287" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2"/>
       <c r="B287" s="2"/>
       <c r="C287" s="2"/>
@@ -11701,7 +11701,7 @@
       <c r="P287" s="3"/>
       <c r="Q287" s="3"/>
     </row>
-    <row r="288" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2"/>
       <c r="B288" s="2"/>
       <c r="C288" s="2"/>
@@ -11720,7 +11720,7 @@
       <c r="P288" s="3"/>
       <c r="Q288" s="3"/>
     </row>
-    <row r="289" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2"/>
       <c r="B289" s="2"/>
       <c r="C289" s="2"/>
@@ -11739,7 +11739,7 @@
       <c r="P289" s="3"/>
       <c r="Q289" s="3"/>
     </row>
-    <row r="290" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2"/>
       <c r="B290" s="2"/>
       <c r="C290" s="2"/>
@@ -11758,7 +11758,7 @@
       <c r="P290" s="3"/>
       <c r="Q290" s="3"/>
     </row>
-    <row r="291" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="2"/>
@@ -11777,7 +11777,7 @@
       <c r="P291" s="3"/>
       <c r="Q291" s="3"/>
     </row>
-    <row r="292" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2"/>
       <c r="B292" s="2"/>
       <c r="C292" s="2"/>
@@ -11796,7 +11796,7 @@
       <c r="P292" s="3"/>
       <c r="Q292" s="3"/>
     </row>
-    <row r="293" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2"/>
       <c r="B293" s="2"/>
       <c r="C293" s="2"/>
@@ -11815,7 +11815,7 @@
       <c r="P293" s="3"/>
       <c r="Q293" s="3"/>
     </row>
-    <row r="294" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2"/>
       <c r="B294" s="2"/>
       <c r="C294" s="2"/>
@@ -11834,7 +11834,7 @@
       <c r="P294" s="3"/>
       <c r="Q294" s="3"/>
     </row>
-    <row r="295" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2"/>
       <c r="B295" s="2"/>
       <c r="C295" s="2"/>
@@ -11853,7 +11853,7 @@
       <c r="P295" s="3"/>
       <c r="Q295" s="3"/>
     </row>
-    <row r="296" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2"/>
       <c r="B296" s="2"/>
       <c r="C296" s="2"/>
@@ -11872,7 +11872,7 @@
       <c r="P296" s="3"/>
       <c r="Q296" s="3"/>
     </row>
-    <row r="297" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2"/>
       <c r="B297" s="2"/>
       <c r="C297" s="2"/>
@@ -11891,7 +11891,7 @@
       <c r="P297" s="3"/>
       <c r="Q297" s="3"/>
     </row>
-    <row r="298" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2"/>
       <c r="B298" s="2"/>
       <c r="C298" s="2"/>
@@ -11910,7 +11910,7 @@
       <c r="P298" s="3"/>
       <c r="Q298" s="3"/>
     </row>
-    <row r="299" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2"/>
       <c r="B299" s="2"/>
       <c r="C299" s="2"/>
@@ -11929,7 +11929,7 @@
       <c r="P299" s="3"/>
       <c r="Q299" s="3"/>
     </row>
-    <row r="300" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2"/>
       <c r="B300" s="2"/>
       <c r="C300" s="2"/>
@@ -11948,7 +11948,7 @@
       <c r="P300" s="3"/>
       <c r="Q300" s="3"/>
     </row>
-    <row r="301" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2"/>
       <c r="B301" s="2"/>
       <c r="C301" s="2"/>
@@ -11967,7 +11967,7 @@
       <c r="P301" s="3"/>
       <c r="Q301" s="3"/>
     </row>
-    <row r="302" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2"/>
       <c r="B302" s="2"/>
       <c r="C302" s="2"/>
@@ -11986,7 +11986,7 @@
       <c r="P302" s="3"/>
       <c r="Q302" s="3"/>
     </row>
-    <row r="303" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2"/>
       <c r="B303" s="2"/>
       <c r="C303" s="2"/>
@@ -12005,7 +12005,7 @@
       <c r="P303" s="3"/>
       <c r="Q303" s="3"/>
     </row>
-    <row r="304" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2"/>
       <c r="B304" s="2"/>
       <c r="C304" s="2"/>
@@ -12024,7 +12024,7 @@
       <c r="P304" s="3"/>
       <c r="Q304" s="3"/>
     </row>
-    <row r="305" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2"/>
       <c r="B305" s="2"/>
       <c r="C305" s="2"/>
@@ -12043,7 +12043,7 @@
       <c r="P305" s="3"/>
       <c r="Q305" s="3"/>
     </row>
-    <row r="306" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2"/>
       <c r="B306" s="2"/>
       <c r="C306" s="2"/>
@@ -12062,7 +12062,7 @@
       <c r="P306" s="5"/>
       <c r="Q306" s="5"/>
     </row>
-    <row r="307" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2"/>
       <c r="B307" s="2"/>
       <c r="C307" s="2"/>
@@ -12081,7 +12081,7 @@
       <c r="P307" s="5"/>
       <c r="Q307" s="5"/>
     </row>
-    <row r="308" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2"/>
       <c r="B308" s="2"/>
       <c r="C308" s="2"/>
@@ -12100,7 +12100,7 @@
       <c r="P308" s="5"/>
       <c r="Q308" s="5"/>
     </row>
-    <row r="309" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2"/>
       <c r="B309" s="2"/>
       <c r="C309" s="2"/>
@@ -12119,7 +12119,7 @@
       <c r="P309" s="5"/>
       <c r="Q309" s="5"/>
     </row>
-    <row r="310" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2"/>
       <c r="B310" s="2"/>
       <c r="C310" s="2"/>
@@ -12138,7 +12138,7 @@
       <c r="P310" s="5"/>
       <c r="Q310" s="5"/>
     </row>
-    <row r="311" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2"/>
       <c r="B311" s="2"/>
       <c r="C311" s="2"/>
@@ -12157,7 +12157,7 @@
       <c r="P311" s="5"/>
       <c r="Q311" s="5"/>
     </row>
-    <row r="312" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2"/>
       <c r="B312" s="2"/>
       <c r="C312" s="2"/>
@@ -12176,7 +12176,7 @@
       <c r="P312" s="5"/>
       <c r="Q312" s="5"/>
     </row>
-    <row r="313" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2"/>
       <c r="B313" s="2"/>
       <c r="C313" s="2"/>
@@ -12195,7 +12195,7 @@
       <c r="P313" s="5"/>
       <c r="Q313" s="5"/>
     </row>
-    <row r="314" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2"/>
       <c r="B314" s="2"/>
       <c r="C314" s="2"/>
@@ -12214,7 +12214,7 @@
       <c r="P314" s="3"/>
       <c r="Q314" s="3"/>
     </row>
-    <row r="315" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2"/>
       <c r="B315" s="2"/>
       <c r="C315" s="2"/>
@@ -12233,7 +12233,7 @@
       <c r="P315" s="3"/>
       <c r="Q315" s="3"/>
     </row>
-    <row r="316" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2"/>
       <c r="B316" s="2"/>
       <c r="C316" s="2"/>
@@ -12252,7 +12252,7 @@
       <c r="P316" s="3"/>
       <c r="Q316" s="3"/>
     </row>
-    <row r="317" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2"/>
       <c r="B317" s="2"/>
       <c r="C317" s="2"/>
@@ -12271,7 +12271,7 @@
       <c r="P317" s="3"/>
       <c r="Q317" s="3"/>
     </row>
-    <row r="318" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2"/>
       <c r="B318" s="2"/>
       <c r="C318" s="2"/>
@@ -12290,7 +12290,7 @@
       <c r="P318" s="3"/>
       <c r="Q318" s="3"/>
     </row>
-    <row r="319" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2"/>
       <c r="B319" s="2"/>
       <c r="C319" s="2"/>
@@ -12309,7 +12309,7 @@
       <c r="P319" s="3"/>
       <c r="Q319" s="3"/>
     </row>
-    <row r="320" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2"/>
       <c r="B320" s="2"/>
       <c r="C320" s="2"/>
@@ -12328,7 +12328,7 @@
       <c r="P320" s="3"/>
       <c r="Q320" s="3"/>
     </row>
-    <row r="321" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2"/>
       <c r="B321" s="2"/>
       <c r="C321" s="2"/>
@@ -12362,9 +12362,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3552810-31BB-4B88-9769-989F9422D843}">
   <dimension ref="A1:Q161"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>21</v>
       </c>
@@ -12417,7 +12417,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -12470,7 +12470,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -12523,7 +12523,7 @@
         <v>272.5</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -12576,7 +12576,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -12629,7 +12629,7 @@
         <v>332.5</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -12664,25 +12664,25 @@
         <v>260</v>
       </c>
       <c r="L6" s="3">
-        <v>285</v>
+        <v>327.5</v>
       </c>
       <c r="M6" s="3">
-        <v>317.5</v>
+        <v>335</v>
       </c>
       <c r="N6" s="3">
-        <v>327.5</v>
+        <v>342.5</v>
       </c>
       <c r="O6" s="3">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="P6" s="3">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="Q6" s="3">
-        <v>392.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -12735,7 +12735,7 @@
         <v>342.5</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
@@ -12788,7 +12788,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -12841,7 +12841,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
@@ -12894,7 +12894,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
@@ -12947,7 +12947,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>7</v>
       </c>
@@ -13000,7 +13000,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
@@ -13053,7 +13053,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>9</v>
       </c>
@@ -13106,7 +13106,7 @@
         <v>422.5</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>10</v>
       </c>
@@ -13159,7 +13159,7 @@
         <v>372.5</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>11</v>
       </c>
@@ -13212,7 +13212,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>12</v>
       </c>
@@ -13265,7 +13265,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>5</v>
       </c>
@@ -13318,7 +13318,7 @@
         <v>322.5</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
@@ -13371,7 +13371,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>7</v>
       </c>
@@ -13424,7 +13424,7 @@
         <v>357.5</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>8</v>
       </c>
@@ -13477,7 +13477,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>9</v>
       </c>
@@ -13530,7 +13530,7 @@
         <v>487.5</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>10</v>
       </c>
@@ -13583,7 +13583,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>11</v>
       </c>
@@ -13636,7 +13636,7 @@
         <v>387.5</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>12</v>
       </c>
@@ -13689,7 +13689,7 @@
         <v>352.5</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>5</v>
       </c>
@@ -13742,7 +13742,7 @@
         <v>337.5</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>6</v>
       </c>
@@ -13795,7 +13795,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>7</v>
       </c>
@@ -13848,7 +13848,7 @@
         <v>372.5</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>8</v>
       </c>
@@ -13901,7 +13901,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>9</v>
       </c>
@@ -13954,7 +13954,7 @@
         <v>507.5</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>10</v>
       </c>
@@ -14007,7 +14007,7 @@
         <v>447.5</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>11</v>
       </c>
@@ -14060,7 +14060,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>12</v>
       </c>
@@ -14113,7 +14113,7 @@
         <v>367.5</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>5</v>
       </c>
@@ -14166,7 +14166,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>6</v>
       </c>
@@ -14219,7 +14219,7 @@
         <v>257.5</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>7</v>
       </c>
@@ -14272,7 +14272,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>8</v>
       </c>
@@ -14325,7 +14325,7 @@
         <v>352.5</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>9</v>
       </c>
@@ -14378,7 +14378,7 @@
         <v>417.5</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>10</v>
       </c>
@@ -14431,7 +14431,7 @@
         <v>342.5</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>11</v>
       </c>
@@ -14484,7 +14484,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>12</v>
       </c>
@@ -14537,7 +14537,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>5</v>
       </c>
@@ -14590,7 +14590,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>6</v>
       </c>
@@ -14643,7 +14643,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>7</v>
       </c>
@@ -14696,7 +14696,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>8</v>
       </c>
@@ -14749,7 +14749,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>9</v>
       </c>
@@ -14802,7 +14802,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>10</v>
       </c>
@@ -14855,7 +14855,7 @@
         <v>392.5</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>11</v>
       </c>
@@ -14908,7 +14908,7 @@
         <v>352.5</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>12</v>
       </c>
@@ -14961,7 +14961,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>5</v>
       </c>
@@ -15014,7 +15014,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>6</v>
       </c>
@@ -15067,7 +15067,7 @@
         <v>292.5</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>7</v>
       </c>
@@ -15120,7 +15120,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>8</v>
       </c>
@@ -15173,7 +15173,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>9</v>
       </c>
@@ -15226,7 +15226,7 @@
         <v>447.5</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>10</v>
       </c>
@@ -15279,7 +15279,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>11</v>
       </c>
@@ -15332,7 +15332,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>12</v>
       </c>
@@ -15385,7 +15385,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>5</v>
       </c>
@@ -15438,7 +15438,7 @@
         <v>277.5</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>6</v>
       </c>
@@ -15491,7 +15491,7 @@
         <v>307.5</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>7</v>
       </c>
@@ -15544,7 +15544,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>8</v>
       </c>
@@ -15597,7 +15597,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>9</v>
       </c>
@@ -15650,7 +15650,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>10</v>
       </c>
@@ -15703,7 +15703,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>11</v>
       </c>
@@ -15756,7 +15756,7 @@
         <v>372.5</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>12</v>
       </c>
@@ -15809,7 +15809,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>5</v>
       </c>
@@ -15862,7 +15862,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>6</v>
       </c>
@@ -15915,7 +15915,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>7</v>
       </c>
@@ -15968,7 +15968,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>8</v>
       </c>
@@ -16021,7 +16021,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>9</v>
       </c>
@@ -16074,7 +16074,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>10</v>
       </c>
@@ -16127,7 +16127,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>11</v>
       </c>
@@ -16180,7 +16180,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>12</v>
       </c>
@@ -16233,7 +16233,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>5</v>
       </c>
@@ -16286,7 +16286,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>6</v>
       </c>
@@ -16339,7 +16339,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>7</v>
       </c>
@@ -16392,7 +16392,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>8</v>
       </c>
@@ -16445,7 +16445,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>9</v>
       </c>
@@ -16498,7 +16498,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>10</v>
       </c>
@@ -16551,7 +16551,7 @@
         <v>77.5</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>11</v>
       </c>
@@ -16604,7 +16604,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>12</v>
       </c>
@@ -16657,7 +16657,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>5</v>
       </c>
@@ -16710,7 +16710,7 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>6</v>
       </c>
@@ -16763,7 +16763,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>7</v>
       </c>
@@ -16816,7 +16816,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>8</v>
       </c>
@@ -16869,7 +16869,7 @@
         <v>77.5</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>9</v>
       </c>
@@ -16922,7 +16922,7 @@
         <v>92.5</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>10</v>
       </c>
@@ -16975,7 +16975,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>11</v>
       </c>
@@ -17028,7 +17028,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>12</v>
       </c>
@@ -17081,7 +17081,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>5</v>
       </c>
@@ -17134,7 +17134,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>6</v>
       </c>
@@ -17187,7 +17187,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>7</v>
       </c>
@@ -17240,7 +17240,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>8</v>
       </c>
@@ -17293,7 +17293,7 @@
         <v>142.5</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>9</v>
       </c>
@@ -17346,7 +17346,7 @@
         <v>167.5</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>10</v>
       </c>
@@ -17399,7 +17399,7 @@
         <v>147.5</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>11</v>
       </c>
@@ -17452,7 +17452,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>12</v>
       </c>
@@ -17505,7 +17505,7 @@
         <v>122.5</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>5</v>
       </c>
@@ -17558,7 +17558,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>6</v>
       </c>
@@ -17611,7 +17611,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>7</v>
       </c>
@@ -17664,7 +17664,7 @@
         <v>127.5</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>8</v>
       </c>
@@ -17717,7 +17717,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>9</v>
       </c>
@@ -17770,7 +17770,7 @@
         <v>177.5</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>10</v>
       </c>
@@ -17823,7 +17823,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>11</v>
       </c>
@@ -17876,7 +17876,7 @@
         <v>142.5</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>12</v>
       </c>
@@ -17929,7 +17929,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>5</v>
       </c>
@@ -17982,7 +17982,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>6</v>
       </c>
@@ -18035,7 +18035,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>7</v>
       </c>
@@ -18088,7 +18088,7 @@
         <v>132.5</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>8</v>
       </c>
@@ -18141,7 +18141,7 @@
         <v>157.5</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>9</v>
       </c>
@@ -18194,7 +18194,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>10</v>
       </c>
@@ -18247,7 +18247,7 @@
         <v>162.5</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>11</v>
       </c>
@@ -18300,7 +18300,7 @@
         <v>147.5</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>12</v>
       </c>
@@ -18353,7 +18353,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>5</v>
       </c>
@@ -18406,7 +18406,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>6</v>
       </c>
@@ -18459,7 +18459,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>7</v>
       </c>
@@ -18512,7 +18512,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>8</v>
       </c>
@@ -18565,7 +18565,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>9</v>
       </c>
@@ -18618,7 +18618,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>10</v>
       </c>
@@ -18671,7 +18671,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>11</v>
       </c>
@@ -18724,7 +18724,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>12</v>
       </c>
@@ -18777,7 +18777,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>5</v>
       </c>
@@ -18830,7 +18830,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>6</v>
       </c>
@@ -18883,7 +18883,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>7</v>
       </c>
@@ -18936,7 +18936,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>8</v>
       </c>
@@ -18989,7 +18989,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>9</v>
       </c>
@@ -19042,7 +19042,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>10</v>
       </c>
@@ -19095,7 +19095,7 @@
         <v>77.5</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>11</v>
       </c>
@@ -19148,7 +19148,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>12</v>
       </c>
@@ -19201,7 +19201,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>5</v>
       </c>
@@ -19254,7 +19254,7 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>6</v>
       </c>
@@ -19307,7 +19307,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>7</v>
       </c>
@@ -19360,7 +19360,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>8</v>
       </c>
@@ -19413,7 +19413,7 @@
         <v>77.5</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>9</v>
       </c>
@@ -19466,7 +19466,7 @@
         <v>92.5</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>10</v>
       </c>
@@ -19519,7 +19519,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>11</v>
       </c>
@@ -19572,7 +19572,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>12</v>
       </c>
@@ -19625,7 +19625,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>5</v>
       </c>
@@ -19678,7 +19678,7 @@
         <v>102.5</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>6</v>
       </c>
@@ -19731,7 +19731,7 @@
         <v>112.5</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>7</v>
       </c>
@@ -19784,7 +19784,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>8</v>
       </c>
@@ -19837,7 +19837,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>9</v>
       </c>
@@ -19890,7 +19890,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>10</v>
       </c>
@@ -19943,7 +19943,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>11</v>
       </c>
@@ -19996,7 +19996,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>12</v>
       </c>
@@ -20049,7 +20049,7 @@
         <v>122.5</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>5</v>
       </c>
@@ -20102,7 +20102,7 @@
         <v>107.5</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>6</v>
       </c>
@@ -20155,7 +20155,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>7</v>
       </c>
@@ -20208,7 +20208,7 @@
         <v>132.5</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>8</v>
       </c>
@@ -20261,7 +20261,7 @@
         <v>152.5</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>9</v>
       </c>
@@ -20314,7 +20314,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>10</v>
       </c>
@@ -20367,7 +20367,7 @@
         <v>157.5</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>11</v>
       </c>
@@ -20420,7 +20420,7 @@
         <v>142.5</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>12</v>
       </c>
@@ -20473,7 +20473,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>5</v>
       </c>
@@ -20526,7 +20526,7 @@
         <v>112.5</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>6</v>
       </c>
@@ -20579,7 +20579,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>7</v>
       </c>
@@ -20632,7 +20632,7 @@
         <v>137.5</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>8</v>
       </c>
@@ -20685,7 +20685,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>9</v>
       </c>
@@ -20738,7 +20738,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>10</v>
       </c>
@@ -20791,7 +20791,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>11</v>
       </c>
@@ -20844,7 +20844,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>12</v>
       </c>
